--- a/test/excel/keep/struct-open/filter-move-over.xlsx
+++ b/test/excel/keep/struct-open/filter-move-over.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-60271/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-68964/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A278619-F7D3-D641-922D-225463CD746D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4CE8D78-B59A-1A49-A127-67B049BA6E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="Pivot" sheetId="2" r:id="rId2"/>
     <sheet name="Plain" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$C$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -446,6 +449,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/test/excel/keep/struct-open/filter-move-over.xlsx
+++ b/test/excel/keep/struct-open/filter-move-over.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-68964/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-60236/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4CE8D78-B59A-1A49-A127-67B049BA6E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1398402-40F6-8B41-AAD2-849D731D8BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Plain" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
